--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92565311959</v>
+        <v>46157.93088090782</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93088090782</v>
+        <v>46157.93166337946</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93166337946</v>
+        <v>46157.93397308567</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93397308567</v>
+        <v>46157.93714950181</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93714950181</v>
+        <v>46158.28213726539</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28213726539</v>
+        <v>46158.29675035644</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29675035644</v>
+        <v>46158.2981166945</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2981166945</v>
+        <v>46158.33384578599</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33384578599</v>
+        <v>46158.36853848625</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/29. Иновационные технологии (ТКО)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36853848625</v>
+        <v>46158.37284708438</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
